--- a/lorenzo-playwright-kdf/excelFramework/testcases/Theatres/LSTP_Theatres_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/Theatres/LSTP_Theatres_WF001.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tk32\ORBIS PAS UKI-LZO\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\Theatres\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\Theatres\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8F43E58-BC96-4A24-9963-9181148C249B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D7A687-88EB-477C-9DF4-B8BBDB7DCEF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{487B3B7E-C780-4162-A08D-73957CA52C11}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{487B3B7E-C780-4162-A08D-73957CA52C11}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="6" r:id="rId1"/>
@@ -2536,7 +2536,7 @@
         <v>319</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>320</v>

--- a/lorenzo-playwright-kdf/excelFramework/testcases/Theatres/LSTP_Theatres_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/Theatres/LSTP_Theatres_WF001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\Theatres\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2D7A687-88EB-477C-9DF4-B8BBDB7DCEF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB7A0FE0-AD97-41B7-B1F1-D8DC2A060081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{487B3B7E-C780-4162-A08D-73957CA52C11}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="551">
   <si>
     <t>StepNo</t>
   </si>
@@ -1573,18 +1573,12 @@
     <t>wait for popup loading</t>
   </si>
   <si>
-    <t>//Click on Seelct the session</t>
-  </si>
-  <si>
     <t>//Click ok in pop up</t>
   </si>
   <si>
     <t>//Wait for Check-in time to be recorded</t>
   </si>
   <si>
-    <t>//wait for element</t>
-  </si>
-  <si>
     <t>Click on cancel</t>
   </si>
   <si>
@@ -1621,18 +1615,6 @@
     <t xml:space="preserve">Verify the procedure code </t>
   </si>
   <si>
-    <t>//Click on Finish in PDS Sync</t>
-  </si>
-  <si>
-    <t>//Click on Allocate NHS YES</t>
-  </si>
-  <si>
-    <t>//Click on No in Has this person had NHS No pop up</t>
-  </si>
-  <si>
-    <t>//Click OK to add the selected patient to the theatre booking</t>
-  </si>
-  <si>
     <t>Wait for load code procedure</t>
   </si>
   <si>
@@ -1709,6 +1691,21 @@
   </si>
   <si>
     <t>btn_ManageReasonOK1</t>
+  </si>
+  <si>
+    <t>Click on Allocate NHS YES</t>
+  </si>
+  <si>
+    <t>Click on No in Has this person had NHS No pop up</t>
+  </si>
+  <si>
+    <t>Click OK to add the selected patient to the theatre booking</t>
+  </si>
+  <si>
+    <t>Click on Finish in PDS Sync</t>
+  </si>
+  <si>
+    <t>//Click on Select the session</t>
   </si>
 </sst>
 </file>
@@ -2430,15 +2427,15 @@
   <dimension ref="A1:P296"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" customWidth="1"/>
     <col min="2" max="2" width="53.85546875" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" customWidth="1"/>
+    <col min="4" max="4" width="27.140625" customWidth="1"/>
     <col min="5" max="5" width="23.85546875" customWidth="1"/>
     <col min="6" max="6" width="32.5703125" customWidth="1"/>
     <col min="9" max="9" width="19" customWidth="1"/>
-    <col min="10" max="10" width="23" customWidth="1"/>
-    <col min="11" max="11" width="19.28515625" customWidth="1"/>
+    <col min="10" max="10" width="27.140625" customWidth="1"/>
+    <col min="11" max="11" width="33.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -2499,7 +2496,7 @@
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
       <c r="K2" s="5" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -2524,7 +2521,7 @@
       <c r="I3" s="7"/>
       <c r="J3" s="5"/>
       <c r="K3" s="5" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="L3" s="12"/>
     </row>
@@ -2934,7 +2931,7 @@
       <c r="I19" s="7"/>
       <c r="J19" s="5"/>
       <c r="K19" s="5" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="L19" s="12"/>
     </row>
@@ -3139,7 +3136,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>523</v>
+        <v>546</v>
       </c>
       <c r="C28" s="28" t="s">
         <v>359</v>
@@ -3163,7 +3160,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="28" t="s">
-        <v>524</v>
+        <v>547</v>
       </c>
       <c r="C29" s="28" t="s">
         <v>359</v>
@@ -3450,7 +3447,7 @@
       <c r="I40" s="7"/>
       <c r="J40" s="7"/>
       <c r="K40" s="5" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="L40" s="12"/>
     </row>
@@ -3802,7 +3799,7 @@
       <c r="I54" s="7"/>
       <c r="J54" s="27"/>
       <c r="K54" s="5" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="L54" s="12"/>
     </row>
@@ -4276,7 +4273,7 @@
       <c r="I74" s="7"/>
       <c r="J74" s="5"/>
       <c r="K74" s="34" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -4301,7 +4298,7 @@
       <c r="I75" s="7"/>
       <c r="J75" s="5"/>
       <c r="K75" s="34" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="L75" s="12"/>
     </row>
@@ -4327,7 +4324,7 @@
       <c r="I76" s="7"/>
       <c r="J76" s="5"/>
       <c r="K76" s="34" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="L76" s="12"/>
     </row>
@@ -4425,7 +4422,7 @@
       <c r="I80" s="7"/>
       <c r="J80" s="5"/>
       <c r="K80" s="34" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="L80" s="12"/>
     </row>
@@ -4709,7 +4706,7 @@
       <c r="I92" s="7"/>
       <c r="J92" s="7"/>
       <c r="K92" s="34" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
@@ -5030,7 +5027,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="28" t="s">
-        <v>525</v>
+        <v>548</v>
       </c>
       <c r="C106" s="28" t="s">
         <v>12</v>
@@ -5054,7 +5051,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="28" t="s">
-        <v>509</v>
+        <v>271</v>
       </c>
       <c r="C107" s="28" t="s">
         <v>435</v>
@@ -5076,7 +5073,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="28" t="s">
-        <v>522</v>
+        <v>549</v>
       </c>
       <c r="C108" s="28" t="s">
         <v>435</v>
@@ -5395,7 +5392,7 @@
       <c r="I121" s="7"/>
       <c r="J121" s="33"/>
       <c r="K121" s="34" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="L121" s="12"/>
     </row>
@@ -5857,7 +5854,7 @@
       <c r="I140" s="7"/>
       <c r="J140" s="5"/>
       <c r="K140" s="35" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="L140" s="12"/>
     </row>
@@ -6129,7 +6126,7 @@
       <c r="I151" s="7"/>
       <c r="J151" s="7"/>
       <c r="K151" s="35" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="L151" s="12"/>
     </row>
@@ -6384,7 +6381,7 @@
         <v>130</v>
       </c>
       <c r="D162" s="7" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="E162" s="7"/>
       <c r="F162" s="7" t="s">
@@ -6425,7 +6422,7 @@
         <v>163</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>506</v>
+        <v>550</v>
       </c>
       <c r="C164" s="7" t="s">
         <v>130</v>
@@ -6477,19 +6474,19 @@
         <v>130</v>
       </c>
       <c r="D166" s="7" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="E166" s="36"/>
       <c r="F166" s="7" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="G166" s="28"/>
       <c r="H166" s="28"/>
       <c r="I166" s="28" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="J166" s="7" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="29"/>
@@ -6719,7 +6716,7 @@
         <v>175</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="C176" s="7" t="s">
         <v>130</v>
@@ -6728,7 +6725,7 @@
         <v>465</v>
       </c>
       <c r="E176" s="7" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="F176" s="7" t="s">
         <v>16</v>
@@ -7321,7 +7318,7 @@
         <v>201</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="C202" s="7" t="s">
         <v>130</v>
@@ -7352,7 +7349,7 @@
         <v>130</v>
       </c>
       <c r="D203" s="7" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="E203" s="7"/>
       <c r="F203" s="7" t="s">
@@ -7390,7 +7387,7 @@
         <v>204</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="C205" s="7" t="s">
         <v>130</v>
@@ -7416,7 +7413,7 @@
         <v>205</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C206" s="7" t="s">
         <v>130</v>
@@ -7440,7 +7437,7 @@
         <v>206</v>
       </c>
       <c r="B207" s="7" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C207" s="7" t="s">
         <v>130</v>
@@ -7595,7 +7592,7 @@
       <c r="I213" s="7"/>
       <c r="J213" s="33"/>
       <c r="K213" s="35" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="L213" s="12"/>
     </row>
@@ -8068,7 +8065,7 @@
         <v>233</v>
       </c>
       <c r="B234" s="7" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C234" s="7" t="s">
         <v>130</v>
@@ -8092,7 +8089,7 @@
         <v>234</v>
       </c>
       <c r="B235" s="7" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C235" s="7" t="s">
         <v>130</v>
@@ -8116,7 +8113,7 @@
         <v>235</v>
       </c>
       <c r="B236" s="7" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C236" s="7" t="s">
         <v>130</v>
@@ -8140,7 +8137,7 @@
         <v>236</v>
       </c>
       <c r="B237" s="7" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C237" s="7" t="s">
         <v>130</v>
@@ -8234,7 +8231,7 @@
         <v>240</v>
       </c>
       <c r="B241" s="7" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C241" s="7" t="s">
         <v>130</v>
@@ -8350,7 +8347,7 @@
         <v>245</v>
       </c>
       <c r="B246" s="7" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="C246" s="7" t="s">
         <v>130</v>
@@ -8608,7 +8605,7 @@
         <v>256</v>
       </c>
       <c r="B257" s="7" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C257" s="7" t="s">
         <v>130</v>
@@ -8632,7 +8629,7 @@
         <v>257</v>
       </c>
       <c r="B258" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C258" s="7" t="s">
         <v>130</v>
@@ -8656,7 +8653,7 @@
         <v>258</v>
       </c>
       <c r="B259" s="7" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C259" s="7" t="s">
         <v>130</v>
@@ -8680,7 +8677,7 @@
         <v>259</v>
       </c>
       <c r="B260" s="7" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C260" s="7" t="s">
         <v>130</v>
@@ -8774,7 +8771,7 @@
         <v>263</v>
       </c>
       <c r="B264" s="7" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C264" s="7" t="s">
         <v>130</v>
@@ -8912,7 +8909,7 @@
         <v>269</v>
       </c>
       <c r="B270" s="7" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="C270" s="7" t="s">
         <v>130</v>
@@ -8937,7 +8934,7 @@
         <v>270</v>
       </c>
       <c r="B271" s="7" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="C271" s="7" t="s">
         <v>130</v>
@@ -8958,7 +8955,7 @@
       <c r="I271" s="7"/>
       <c r="J271" s="33"/>
       <c r="K271" s="35" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
     </row>
     <row r="272" spans="1:12" s="29" customFormat="1" x14ac:dyDescent="0.25">
@@ -8972,19 +8969,19 @@
         <v>130</v>
       </c>
       <c r="D272" s="28" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="E272" s="28"/>
       <c r="F272" s="28" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="G272" s="28"/>
       <c r="H272" s="28"/>
       <c r="I272" s="28" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="J272" s="28" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="K272" s="28"/>
     </row>
@@ -9107,7 +9104,7 @@
         <v>277</v>
       </c>
       <c r="B278" s="7" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C278" s="7" t="s">
         <v>130</v>
@@ -9137,7 +9134,7 @@
         <v>278</v>
       </c>
       <c r="B279" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C279" s="7" t="s">
         <v>130</v>
@@ -9402,16 +9399,16 @@
   <sheetData>
     <row r="1" spans="1:35" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="C1" s="10" t="s">
         <v>35</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>356</v>
@@ -9423,28 +9420,28 @@
         <v>55</v>
       </c>
       <c r="H1" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="N1" s="9" t="s">
         <v>536</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="O1" s="9" t="s">
         <v>537</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>538</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>539</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>540</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>541</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>542</v>
-      </c>
-      <c r="O1" s="9" t="s">
-        <v>543</v>
       </c>
       <c r="P1" s="9" t="s">
         <v>370</v>

--- a/lorenzo-playwright-kdf/excelFramework/testcases/Theatres/LSTP_Theatres_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/Theatres/LSTP_Theatres_WF001.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\Theatres\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB7A0FE0-AD97-41B7-B1F1-D8DC2A060081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B03E0594-102B-4C4B-A0FA-49D907DFD876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{487B3B7E-C780-4162-A08D-73957CA52C11}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{487B3B7E-C780-4162-A08D-73957CA52C11}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="6" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="552">
   <si>
     <t>StepNo</t>
   </si>
@@ -1706,6 +1706,9 @@
   </si>
   <si>
     <t>//Click on Select the session</t>
+  </si>
+  <si>
+    <t>launchRegistration</t>
   </si>
 </sst>
 </file>
@@ -2974,7 +2977,7 @@
       </c>
       <c r="E21" s="7"/>
       <c r="F21" s="7" t="s">
-        <v>16</v>
+        <v>551</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
@@ -3050,7 +3053,7 @@
       </c>
       <c r="E24" s="7"/>
       <c r="F24" s="7" t="s">
-        <v>16</v>
+        <v>551</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
